--- a/robot_vision_2026/misc/position_encoding.xlsx
+++ b/robot_vision_2026/misc/position_encoding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ueda/GIT/slides_marp/advanced_vision/misc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ueda/GIT/slides_marp/robot_vision_2026/misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE62734A-A843-DE46-8C26-42680464EEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DAD164-BBEB-B246-AC4A-3089F1697192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="10660" windowWidth="38400" windowHeight="19400" xr2:uid="{6773948F-5FD1-F446-BD98-9D741AB57698}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="17000" xr2:uid="{6773948F-5FD1-F446-BD98-9D741AB57698}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
   <si>
     <t xml:space="preserve">I / j </t>
     <phoneticPr fontId="1"/>
@@ -427,10 +427,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5A0D6E-4C8E-934F-AECC-CCA75DF108C6}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,7 +450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -464,18 +464,18 @@
       </c>
       <c r="D2">
         <f>SIN($A2*(POWER($B$7,-2*D$1/5)))</f>
-        <v>0.15782664013030581</v>
+        <v>6.309573026154194E-4</v>
       </c>
       <c r="E2">
         <f>COS($A2*(POWER($B$7,-2*(E$1-1)/5)))</f>
-        <v>0.98746683572927096</v>
+        <v>0.99999980094642138</v>
       </c>
       <c r="F2">
         <f>SIN($A2*(POWER($B$7,-2*F$1/5)))</f>
-        <v>2.511622290977376E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>3.9810717055348565E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -484,23 +484,23 @@
         <v>0.90929742682568171</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:G5" si="1">COS($A3*(POWER($B$7,-2*(C$1-1)/5)))</f>
+        <f t="shared" ref="C3:E5" si="1">COS($A3*(POWER($B$7,-2*(C$1-1)/5)))</f>
         <v>-0.41614683654714241</v>
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>0.31169714584651093</v>
+        <v>1.2619143540422207E-3</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>0.95018150333035789</v>
+        <v>0.99999920378576457</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
-        <v>5.0216599387465179E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>7.9621434110690819E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -514,18 +514,18 @@
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0.4577545484994926</v>
+        <v>1.8928709030918858E-3</v>
       </c>
       <c r="E4">
         <f t="shared" si="1"/>
-        <v>0.88907860919494952</v>
+        <v>0.99999820851826737</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>7.5285292998888906E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>1.1943215116602045E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -539,23 +539,302 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.59233772524843908</v>
+        <v>2.5238266985760961E-3</v>
       </c>
       <c r="E5">
         <f t="shared" si="1"/>
-        <v>0.80568977854227775</v>
+        <v>0.99999681514432615</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.10030648729934569</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>1.5924286822133118E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>1</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <f>SIN($A10*(POWER($B$7,-2*B$1/5)))</f>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f>COS($A10*(POWER($B$7,-2*(C$1-1)/5)))</f>
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <f>SIN($A10*(POWER($B$7,-2*D$1/5)))</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f>COS($A10*(POWER($B$7,-2*(E$1-1)/5)))</f>
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <f>SIN($A10*(POWER($B$7,-2*F$1/5)))</f>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>B10*B11+C10*C11+D10*D11+E10*E11+F10*F11</f>
+        <v>1.5403021068145613</v>
+      </c>
+      <c r="I10">
+        <f>B10*B12+C10*C12+D10*D12+E10*E12+F10*F12</f>
+        <v>0.58385236723862222</v>
+      </c>
+      <c r="J10">
+        <f>B10*B13+C10*C13+D10*D13+E10*E13+F10*F13</f>
+        <v>1.0005711917821958E-2</v>
+      </c>
+      <c r="K10">
+        <f>B10*B14+C10*C14+D10*D14+E10*E14+F10*F14</f>
+        <v>0.34635319428071421</v>
+      </c>
+      <c r="L10">
+        <f>B10*B15+C10*C15+D10*D15+E10*E15+F10*F15</f>
+        <v>1.2836572091277216</v>
+      </c>
+      <c r="M10">
+        <f>B10*B16+C10*C16+D10*D16+E10*E16+F10*F16</f>
+        <v>1.9601631207298544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <f>SIN($A11*(POWER($B$7,-2*B$1/5)))</f>
+        <v>0.8414709848078965</v>
+      </c>
+      <c r="C11">
+        <f>COS($A11*(POWER($B$7,-2*(C$1-1)/5)))</f>
+        <v>0.54030230586813977</v>
+      </c>
+      <c r="D11">
+        <f>SIN($A11*(POWER($B$7,-2*D$1/5)))</f>
+        <v>6.309573026154194E-4</v>
+      </c>
+      <c r="E11">
+        <f>COS($A11*(POWER($B$7,-2*(E$1-1)/5)))</f>
+        <v>0.99999980094642138</v>
+      </c>
+      <c r="F11">
+        <f>SIN($A11*(POWER($B$7,-2*F$1/5)))</f>
+        <v>3.9810717055348565E-7</v>
+      </c>
+      <c r="H11">
+        <f>B11*B12+C11*C12+D11*D12+E11*E12+F11*F12</f>
+        <v>1.5403021068148783</v>
+      </c>
+      <c r="I11">
+        <f>B11*B13+C11*C13+D11*D13+E11*E13+F11*F13</f>
+        <v>0.58385236723909761</v>
+      </c>
+      <c r="J11">
+        <f>B11*B14+C11*C14+D11*D14+E11*E14+F11*F14</f>
+        <v>1.0005711918455803E-2</v>
+      </c>
+      <c r="K11">
+        <f>B11*B15+C11*C15+D11*D15+E11*E15+F11*F15</f>
+        <v>0.34635319428150674</v>
+      </c>
+      <c r="L11">
+        <f>B11*B16+C11*C16+D11*D16+E11*E16+F11*F16</f>
+        <v>1.2836572091286729</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:F16" si="2">SIN($A12*(POWER($B$7,-2*B$1/5)))</f>
+        <v>0.90929742682568171</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:E16" si="3">COS($A12*(POWER($B$7,-2*(C$1-1)/5)))</f>
+        <v>-0.41614683654714241</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>1.2619143540422207E-3</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>0.99999920378576457</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>7.9621434110690819E-7</v>
+      </c>
+      <c r="H12">
+        <f t="shared" ref="H12:H15" si="4">B12*B13+C12*C13+D12*D13+E12*E13+F12*F13</f>
+        <v>1.5403021068155121</v>
+      </c>
+      <c r="I12">
+        <f>B12*B14+C12*C14+D12*D14+E12*E14+F12*F14</f>
+        <v>0.58385236723989009</v>
+      </c>
+      <c r="J12">
+        <f>B12*B15+C12*C15+D12*D15+E12*E15+F12*F15</f>
+        <v>1.0005711919406962E-2</v>
+      </c>
+      <c r="K12">
+        <f>B12*B16+C12*C16+D12*D16+E12*E16+F12*F16</f>
+        <v>0.34635319428261618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="2"/>
+        <v>0.14112000805986721</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="3"/>
+        <v>-0.98999249660044542</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>1.8928709030918858E-3</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>0.99999820851826737</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>1.1943215116602045E-6</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="4"/>
+        <v>1.5403021068164628</v>
+      </c>
+      <c r="I13">
+        <f>B13*B15+C13*C15+D13*D15+E13*E15+F13*F15</f>
+        <v>0.58385236724099954</v>
+      </c>
+      <c r="J13">
+        <f>B13*B16+C13*C16+D13*D16+E13*E16+F13*F16</f>
+        <v>1.0005711920674877E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="2"/>
+        <v>-0.75680249530792831</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="3"/>
+        <v>-0.65364362086361194</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>2.5238266985760961E-3</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>0.99999681514432615</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>1.5924286822133118E-6</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="4"/>
+        <v>1.5403021068177309</v>
+      </c>
+      <c r="I14">
+        <f>B14*B16+C14*C16+D14*D16+E14*E16+F14*F16</f>
+        <v>0.58385236724242595</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="2"/>
+        <v>-0.95892427466313845</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="3"/>
+        <v>0.28366218546322625</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>3.1547814893068339E-3</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>0.99999502366449544</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>1.9905358527661662E-6</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="4"/>
+        <v>1.5403021068193159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="2"/>
+        <v>-0.27941549819892586</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="3"/>
+        <v>0.96017028665036597</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>3.7857350240964815E-3</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>0.99999283407948847</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>2.3886430233187057E-6</v>
       </c>
     </row>
   </sheetData>

--- a/robot_vision_2026/misc/position_encoding.xlsx
+++ b/robot_vision_2026/misc/position_encoding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ueda/GIT/slides_marp/robot_vision_2026/misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DAD164-BBEB-B246-AC4A-3089F1697192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5042E16-2D3D-9B46-861E-4483DCCF34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="17000" xr2:uid="{6773948F-5FD1-F446-BD98-9D741AB57698}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21200" windowHeight="12020" xr2:uid="{6773948F-5FD1-F446-BD98-9D741AB57698}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -602,6 +602,10 @@
         <f>SIN($A10*(POWER($B$7,-2*F$1/5)))</f>
         <v>0</v>
       </c>
+      <c r="G10">
+        <f>B10*B10+C10*C10+D10*D10+E10*E10+F10*F10</f>
+        <v>2</v>
+      </c>
       <c r="H10">
         <f>B10*B11+C10*C11+D10*D11+E10*E11+F10*F11</f>
         <v>1.5403021068145613</v>
